--- a/data/dividends_info_20260430.xlsx
+++ b/data/dividends_info_20260430.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>44.54499816894531</v>
+        <v>46.01499938964844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.202042886293671</v>
+        <v>0.1955883976828791</v>
       </c>
       <c r="J2" t="n">
         <v>319</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.04999923706055</v>
+        <v>55.75</v>
       </c>
       <c r="I3" t="n">
-        <v>1.271571316441997</v>
+        <v>1.255605381165919</v>
       </c>
       <c r="J3" t="n">
         <v>298</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.479999542236328</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6329114229666515</v>
+        <v>0.6249999751647324</v>
       </c>
       <c r="J4" t="n">
         <v>228</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>44.54499816894531</v>
+        <v>46.01499938964844</v>
       </c>
       <c r="I6" t="n">
-        <v>0.202042886293671</v>
+        <v>0.1955883976828791</v>
       </c>
       <c r="J6" t="n">
         <v>228</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.069999933242798</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="I7" t="n">
-        <v>3.719806883248261</v>
+        <v>3.737864181496264</v>
       </c>
       <c r="J7" t="n">
         <v>207</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.929999828338623</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I8" t="n">
-        <v>3.372681379251118</v>
+        <v>3.378378334839559</v>
       </c>
       <c r="J8" t="n">
         <v>200</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.050000190734863</v>
+        <v>6.25</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9917355059242088</v>
+        <v>0.96</v>
       </c>
       <c r="J9" t="n">
         <v>172</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.949999809265137</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7676767972571169</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J11" t="n">
         <v>151</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>44.54499816894531</v>
+        <v>46.01499938964844</v>
       </c>
       <c r="I12" t="n">
-        <v>0.202042886293671</v>
+        <v>0.1955883976828791</v>
       </c>
       <c r="J12" t="n">
         <v>144</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4.949999809265137</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7676767972571169</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J14" t="n">
         <v>95</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6.090000152587891</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="I15" t="n">
-        <v>4.105090209131846</v>
+        <v>4.111842156859978</v>
       </c>
       <c r="J15" t="n">
         <v>88</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9.673999786376953</v>
+        <v>9.923999786376953</v>
       </c>
       <c r="I16" t="n">
-        <v>2.687616350437957</v>
+        <v>2.619911382474149</v>
       </c>
       <c r="J16" t="n">
         <v>81</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>16.04000091552734</v>
+        <v>16.10000038146973</v>
       </c>
       <c r="I17" t="n">
-        <v>3.740648165544533</v>
+        <v>3.726707986234393</v>
       </c>
       <c r="J17" t="n">
         <v>81</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3.661999940872192</v>
+        <v>3.690000057220459</v>
       </c>
       <c r="I18" t="n">
-        <v>6.007646192031389</v>
+        <v>5.962059528143148</v>
       </c>
       <c r="J18" t="n">
         <v>81</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.804999828338623</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I20" t="n">
-        <v>4.134367047323193</v>
+        <v>4.102564169444617</v>
       </c>
       <c r="J20" t="n">
         <v>81</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5.46999979019165</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="I22" t="n">
-        <v>2.193784362024548</v>
+        <v>2.197802182446978</v>
       </c>
       <c r="J22" t="n">
         <v>74</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.160000085830688</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I24" t="n">
-        <v>3.935185028814982</v>
+        <v>3.971962422114281</v>
       </c>
       <c r="J24" t="n">
         <v>67</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.170000076293945</v>
+        <v>4.039999961853027</v>
       </c>
       <c r="I25" t="n">
-        <v>1.678657043627969</v>
+        <v>1.732673283687189</v>
       </c>
       <c r="J25" t="n">
         <v>67</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>34.09999847412109</v>
+        <v>34</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4398827176307261</v>
+        <v>0.4411764705882353</v>
       </c>
       <c r="J26" t="n">
         <v>67</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>22.26000022888184</v>
+        <v>22.34000015258789</v>
       </c>
       <c r="I28" t="n">
-        <v>4.267744789900751</v>
+        <v>4.252461922610824</v>
       </c>
       <c r="J28" t="n">
         <v>53</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>25.85000038146973</v>
+        <v>26</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7543520198157657</v>
+        <v>0.7500000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>53</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.89799976348877</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I31" t="n">
-        <v>5.92078427936545</v>
+        <v>5.82329315038745</v>
       </c>
       <c r="J31" t="n">
         <v>53</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3.970000028610229</v>
+        <v>4.01800012588501</v>
       </c>
       <c r="I32" t="n">
-        <v>4.03022667120763</v>
+        <v>3.982080512373259</v>
       </c>
       <c r="J32" t="n">
         <v>53</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.569999933242798</v>
+        <v>2.604000091552734</v>
       </c>
       <c r="I33" t="n">
-        <v>5.392996249035542</v>
+        <v>5.322580458027345</v>
       </c>
       <c r="J33" t="n">
         <v>53</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>52.34000015258789</v>
+        <v>53.02000045776367</v>
       </c>
       <c r="I34" t="n">
-        <v>1.203668318997608</v>
+        <v>1.18823084602171</v>
       </c>
       <c r="J34" t="n">
         <v>53</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.019999980926514</v>
+        <v>5.059999942779541</v>
       </c>
       <c r="I35" t="n">
-        <v>2.788844632110158</v>
+        <v>2.766798450260371</v>
       </c>
       <c r="J35" t="n">
         <v>53</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>19.25</v>
+        <v>19.45000076293945</v>
       </c>
       <c r="I36" t="n">
-        <v>4.051948051948052</v>
+        <v>4.010282619043556</v>
       </c>
       <c r="J36" t="n">
         <v>53</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>22.28000068664551</v>
+        <v>22.59000015258789</v>
       </c>
       <c r="I37" t="n">
-        <v>3.815080672369479</v>
+        <v>3.76272684488063</v>
       </c>
       <c r="J37" t="n">
         <v>53</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>44.54499816894531</v>
+        <v>46.01499938964844</v>
       </c>
       <c r="I38" t="n">
-        <v>0.202042886293671</v>
+        <v>0.1955883976828791</v>
       </c>
       <c r="J38" t="n">
         <v>53</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>6.64799976348877</v>
+        <v>6.72599983215332</v>
       </c>
       <c r="I39" t="n">
-        <v>2.727136077767495</v>
+        <v>2.69551002861023</v>
       </c>
       <c r="J39" t="n">
         <v>53</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>8.449999809265137</v>
+        <v>8.430000305175781</v>
       </c>
       <c r="I40" t="n">
-        <v>3.076923146375919</v>
+        <v>3.084222901396188</v>
       </c>
       <c r="J40" t="n">
         <v>53</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>10.15999984741211</v>
+        <v>10.25</v>
       </c>
       <c r="I41" t="n">
-        <v>2.726377993701995</v>
+        <v>2.702439024390244</v>
       </c>
       <c r="J41" t="n">
         <v>53</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.139999985694885</v>
+        <v>1.149999976158142</v>
       </c>
       <c r="I42" t="n">
-        <v>1.184210541175673</v>
+        <v>1.173913067815886</v>
       </c>
       <c r="J42" t="n">
         <v>46</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>4.119999885559082</v>
+        <v>3.970000028610229</v>
       </c>
       <c r="I43" t="n">
-        <v>2.669902986783046</v>
+        <v>2.770780836455245</v>
       </c>
       <c r="J43" t="n">
         <v>46</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3.420000076293945</v>
+        <v>3.474999904632568</v>
       </c>
       <c r="I45" t="n">
-        <v>4.678362468733704</v>
+        <v>4.604316673122836</v>
       </c>
       <c r="J45" t="n">
         <v>39</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.9100000262260437</v>
+        <v>0.8899999856948853</v>
       </c>
       <c r="I46" t="n">
-        <v>2.747252668077397</v>
+        <v>2.808988809194278</v>
       </c>
       <c r="J46" t="n">
         <v>39</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>27.79999923706055</v>
+        <v>27.89999961853027</v>
       </c>
       <c r="I47" t="n">
-        <v>3.99280586497371</v>
+        <v>3.978494678052877</v>
       </c>
       <c r="J47" t="n">
         <v>35</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.9010000228881836</v>
+        <v>0.9029999971389771</v>
       </c>
       <c r="I48" t="n">
-        <v>3.329633655705586</v>
+        <v>3.322259146738714</v>
       </c>
       <c r="J48" t="n">
         <v>32</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.5040000081062317</v>
+        <v>0.5070000290870667</v>
       </c>
       <c r="I49" t="n">
-        <v>4.563491990093802</v>
+        <v>4.536488891611135</v>
       </c>
       <c r="J49" t="n">
         <v>32</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>19</v>
+        <v>19.25</v>
       </c>
       <c r="I50" t="n">
-        <v>3.157894736842105</v>
+        <v>3.116883116883117</v>
       </c>
       <c r="J50" t="n">
         <v>32</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>9.159999847412109</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I51" t="n">
-        <v>2.183406149908443</v>
+        <v>2.197802105670883</v>
       </c>
       <c r="J51" t="n">
         <v>32</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>8.949999809265137</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I53" t="n">
-        <v>3.35195537869662</v>
+        <v>3.370786661331805</v>
       </c>
       <c r="J53" t="n">
         <v>25</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>13.02000045776367</v>
+        <v>13.09000015258789</v>
       </c>
       <c r="I54" t="n">
-        <v>1.920122820356185</v>
+        <v>1.909854828768471</v>
       </c>
       <c r="J54" t="n">
         <v>25</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>3.339999914169312</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8982036158962379</v>
+        <v>0.9009009215415272</v>
       </c>
       <c r="J55" t="n">
         <v>25</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>3.769999980926514</v>
+        <v>3.819999933242798</v>
       </c>
       <c r="I56" t="n">
-        <v>3.978779860978569</v>
+        <v>3.926701639302517</v>
       </c>
       <c r="J56" t="n">
         <v>25</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>13.85000038146973</v>
+        <v>13.64999961853027</v>
       </c>
       <c r="I57" t="n">
-        <v>4.187725516426678</v>
+        <v>4.249084367831286</v>
       </c>
       <c r="J57" t="n">
         <v>25</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2.355000019073486</v>
+        <v>2.424999952316284</v>
       </c>
       <c r="I58" t="n">
-        <v>4.416135845337109</v>
+        <v>4.288659878144016</v>
       </c>
       <c r="J58" t="n">
         <v>18</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>9.27400016784668</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I59" t="n">
-        <v>3.127021724729328</v>
+        <v>3.085106508178163</v>
       </c>
       <c r="J59" t="n">
         <v>18</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>2.069999933242798</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="I60" t="n">
-        <v>3.719806883248261</v>
+        <v>3.737864181496264</v>
       </c>
       <c r="J60" t="n">
         <v>18</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>37.5</v>
+        <v>38.09999847412109</v>
       </c>
       <c r="I61" t="n">
-        <v>4.373333333333333</v>
+        <v>4.304462114647977</v>
       </c>
       <c r="J61" t="n">
         <v>18</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>35.70999908447266</v>
+        <v>36.09999847412109</v>
       </c>
       <c r="I62" t="n">
-        <v>5.600672224238829</v>
+        <v>5.540166439158535</v>
       </c>
       <c r="J62" t="n">
         <v>18</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>3.891999959945679</v>
+        <v>3.924000024795532</v>
       </c>
       <c r="I63" t="n">
-        <v>2.569373099412769</v>
+        <v>2.54841996350932</v>
       </c>
       <c r="J63" t="n">
         <v>18</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>31.07999992370605</v>
+        <v>31.54000091552734</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4776705288430942</v>
+        <v>0.4707038544406389</v>
       </c>
       <c r="J64" t="n">
         <v>18</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>22.92000007629395</v>
+        <v>23.20000076293945</v>
       </c>
       <c r="I65" t="n">
-        <v>4.013961592223344</v>
+        <v>3.965517110972006</v>
       </c>
       <c r="J65" t="n">
         <v>18</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>7.960000038146973</v>
+        <v>8</v>
       </c>
       <c r="I66" t="n">
-        <v>3.76884420304397</v>
+        <v>3.75</v>
       </c>
       <c r="J66" t="n">
         <v>18</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>80.72000122070312</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="I67" t="n">
-        <v>1.288404341269088</v>
+        <v>1.256645690134306</v>
       </c>
       <c r="J67" t="n">
         <v>18</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>45.54999923706055</v>
+        <v>46.52000045776367</v>
       </c>
       <c r="I68" t="n">
-        <v>1.536772802908114</v>
+        <v>1.504729133946467</v>
       </c>
       <c r="J68" t="n">
         <v>18</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>55.04999923706055</v>
+        <v>55.75</v>
       </c>
       <c r="I69" t="n">
-        <v>3.996366994531991</v>
+        <v>3.946188340807175</v>
       </c>
       <c r="J69" t="n">
         <v>18</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>8.970000267028809</v>
+        <v>9.052000045776367</v>
       </c>
       <c r="I70" t="n">
-        <v>9.58751364992839</v>
+        <v>9.500662788896836</v>
       </c>
       <c r="J70" t="n">
         <v>18</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>12.27000045776367</v>
+        <v>12.53400039672852</v>
       </c>
       <c r="I71" t="n">
-        <v>4.563977009843287</v>
+        <v>4.46784731350547</v>
       </c>
       <c r="J71" t="n">
         <v>18</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>9.760000228881836</v>
+        <v>9.770000457763672</v>
       </c>
       <c r="I73" t="n">
-        <v>3.073770419720264</v>
+        <v>3.070624216415535</v>
       </c>
       <c r="J73" t="n">
         <v>18</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>75.80000305175781</v>
+        <v>77.90000152587891</v>
       </c>
       <c r="I75" t="n">
-        <v>2.717677990848351</v>
+        <v>2.644415866045464</v>
       </c>
       <c r="J75" t="n">
         <v>18</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>14.96000003814697</v>
+        <v>15.0600004196167</v>
       </c>
       <c r="I76" t="n">
-        <v>5.013368971173473</v>
+        <v>4.980079542514971</v>
       </c>
       <c r="J76" t="n">
         <v>18</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>14.93000030517578</v>
+        <v>15.14999961853027</v>
       </c>
       <c r="I77" t="n">
-        <v>2.009377052028586</v>
+        <v>1.980198069662417</v>
       </c>
       <c r="J77" t="n">
         <v>18</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>45.59999847412109</v>
+        <v>46.20000076293945</v>
       </c>
       <c r="I78" t="n">
-        <v>1.864035150094121</v>
+        <v>1.839826809444232</v>
       </c>
       <c r="J78" t="n">
         <v>18</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>32.81999969482422</v>
+        <v>33.04000091552734</v>
       </c>
       <c r="I79" t="n">
-        <v>2.58988424102285</v>
+        <v>2.572639153894628</v>
       </c>
       <c r="J79" t="n">
         <v>18</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>56.45999908447266</v>
+        <v>58.02000045776367</v>
       </c>
       <c r="I80" t="n">
-        <v>2.302515092242571</v>
+        <v>2.240606669671349</v>
       </c>
       <c r="J80" t="n">
         <v>18</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>8.119999885559082</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I81" t="n">
-        <v>7.389162665717064</v>
+        <v>7.407407058555364</v>
       </c>
       <c r="J81" t="n">
         <v>18</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>5.849999904632568</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I82" t="n">
-        <v>8.034188165162375</v>
+        <v>7.966101566151415</v>
       </c>
       <c r="J82" t="n">
         <v>18</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>5.929999828338623</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I83" t="n">
-        <v>3.372681379251118</v>
+        <v>3.378378334839559</v>
       </c>
       <c r="J83" t="n">
         <v>18</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>22.70000076293945</v>
+        <v>22.97999954223633</v>
       </c>
       <c r="I84" t="n">
-        <v>4.40528619555213</v>
+        <v>4.351610182419889</v>
       </c>
       <c r="J84" t="n">
         <v>18</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>4.869999885559082</v>
+        <v>4.71999979019165</v>
       </c>
       <c r="I85" t="n">
-        <v>4.414784497994249</v>
+        <v>4.555084948240435</v>
       </c>
       <c r="J85" t="n">
         <v>18</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>23.90500068664551</v>
+        <v>24</v>
       </c>
       <c r="I86" t="n">
-        <v>1.129470789560927</v>
+        <v>1.125</v>
       </c>
       <c r="J86" t="n">
         <v>18</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>8.399999618530273</v>
+        <v>8.439999580383301</v>
       </c>
       <c r="I87" t="n">
-        <v>2.380952489078726</v>
+        <v>2.369668364259765</v>
       </c>
       <c r="J87" t="n">
         <v>18</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>9.25</v>
+        <v>9.300000190734863</v>
       </c>
       <c r="I88" t="n">
-        <v>2.594594594594594</v>
+        <v>2.580645108363549</v>
       </c>
       <c r="J88" t="n">
         <v>18</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>20.79999923706055</v>
+        <v>21.07999992370605</v>
       </c>
       <c r="I89" t="n">
-        <v>3.79807706238956</v>
+        <v>3.747628097055092</v>
       </c>
       <c r="J89" t="n">
         <v>18</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5.260000228881836</v>
+        <v>5.119999885559082</v>
       </c>
       <c r="I90" t="n">
-        <v>1.768060759567112</v>
+        <v>1.816406290599844</v>
       </c>
       <c r="J90" t="n">
         <v>18</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>6.050000190734863</v>
+        <v>6.25</v>
       </c>
       <c r="I91" t="n">
-        <v>0.9917355059242088</v>
+        <v>0.96</v>
       </c>
       <c r="J91" t="n">
         <v>18</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>35.56000137329102</v>
+        <v>35.77999877929688</v>
       </c>
       <c r="I92" t="n">
-        <v>0.984251930493129</v>
+        <v>0.978200145167467</v>
       </c>
       <c r="J92" t="n">
         <v>18</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>7.28000020980835</v>
+        <v>7.224999904632568</v>
       </c>
       <c r="I93" t="n">
-        <v>7.614010769576507</v>
+        <v>7.67197241960641</v>
       </c>
       <c r="J93" t="n">
         <v>18</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>2.210000038146973</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I94" t="n">
-        <v>2.71493207983419</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J94" t="n">
         <v>18</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>12.5</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>1.587301539245438</v>
       </c>
       <c r="J95" t="n">
         <v>18</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>6.085000038146973</v>
+        <v>6.190000057220459</v>
       </c>
       <c r="I96" t="n">
-        <v>1.692686924474794</v>
+        <v>1.663974136476031</v>
       </c>
       <c r="J96" t="n">
         <v>18</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.633999824523926</v>
+        <v>5.775000095367432</v>
       </c>
       <c r="I97" t="n">
-        <v>3.372382071667087</v>
+        <v>3.290043235712039</v>
       </c>
       <c r="J97" t="n">
         <v>18</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>10.16499996185303</v>
+        <v>10.28999996185303</v>
       </c>
       <c r="I98" t="n">
-        <v>4.249877044969989</v>
+        <v>4.198250744426682</v>
       </c>
       <c r="J98" t="n">
         <v>18</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>24.95000076293945</v>
+        <v>25.07999992370605</v>
       </c>
       <c r="I99" t="n">
-        <v>1.76352700018179</v>
+        <v>1.754385970249164</v>
       </c>
       <c r="J99" t="n">
         <v>18</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>8.489999771118164</v>
+        <v>8.590000152587891</v>
       </c>
       <c r="I101" t="n">
-        <v>5.535924766439649</v>
+        <v>5.471478366137212</v>
       </c>
       <c r="J101" t="n">
         <v>18</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>51.29999923706055</v>
+        <v>51.2400016784668</v>
       </c>
       <c r="I102" t="n">
-        <v>2.729044874894659</v>
+        <v>2.732240347658573</v>
       </c>
       <c r="J102" t="n">
         <v>18</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>3.908999919891357</v>
+        <v>4.047999858856201</v>
       </c>
       <c r="I103" t="n">
-        <v>7.674597240931585</v>
+        <v>7.411067452081574</v>
       </c>
       <c r="J103" t="n">
         <v>18</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>11.94999980926514</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="I104" t="n">
-        <v>1.004184116446269</v>
+        <v>0.9836065727547595</v>
       </c>
       <c r="J104" t="n">
         <v>18</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>21.04999923706055</v>
+        <v>21.79999923706055</v>
       </c>
       <c r="I106" t="n">
-        <v>3.325415797486504</v>
+        <v>3.211009286688334</v>
       </c>
       <c r="J106" t="n">
         <v>18</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>2.579999923706055</v>
+        <v>2.539999961853027</v>
       </c>
       <c r="I107" t="n">
-        <v>1.356589187402923</v>
+        <v>1.377952776600286</v>
       </c>
       <c r="J107" t="n">
         <v>18</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0.9629999995231628</v>
+        <v>0.9660000205039978</v>
       </c>
       <c r="I109" t="n">
-        <v>7.268951197784119</v>
+        <v>7.246376657784999</v>
       </c>
       <c r="J109" t="n">
         <v>18</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>49.31999969482422</v>
+        <v>49.63999938964844</v>
       </c>
       <c r="I110" t="n">
-        <v>1.439578273303415</v>
+        <v>1.430298164242238</v>
       </c>
       <c r="J110" t="n">
         <v>18</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>94.59999847412109</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="I111" t="n">
-        <v>1.427061333800452</v>
+        <v>1.431601226204664</v>
       </c>
       <c r="J111" t="n">
         <v>18</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>7.179999828338623</v>
+        <v>7</v>
       </c>
       <c r="I112" t="n">
-        <v>1.114206154772446</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="J112" t="n">
         <v>18</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>4.502999782562256</v>
+        <v>4.605999946594238</v>
       </c>
       <c r="I114" t="n">
-        <v>3.775261119450203</v>
+        <v>3.690838080137217</v>
       </c>
       <c r="J114" t="n">
         <v>18</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>7.699999809265137</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="I115" t="n">
-        <v>3.857142952687225</v>
+        <v>3.933774735058545</v>
       </c>
       <c r="J115" t="n">
         <v>18</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>58.09999847412109</v>
+        <v>57.59999847412109</v>
       </c>
       <c r="I116" t="n">
-        <v>0.7745266984825121</v>
+        <v>0.7812500206960578</v>
       </c>
       <c r="J116" t="n">
         <v>18</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>4.760000228881836</v>
+        <v>4.869999885559082</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8403360940467085</v>
+        <v>0.8213552554407904</v>
       </c>
       <c r="J117" t="n">
         <v>18</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>32.90000152587891</v>
+        <v>33.20000076293945</v>
       </c>
       <c r="I118" t="n">
-        <v>3.191489213683099</v>
+        <v>3.162650529731601</v>
       </c>
       <c r="J118" t="n">
         <v>18</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>20.15999984741211</v>
+        <v>20.04000091552734</v>
       </c>
       <c r="I120" t="n">
-        <v>1.884920649187305</v>
+        <v>1.896207498202105</v>
       </c>
       <c r="J120" t="n">
         <v>18</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>26.93000030517578</v>
+        <v>27.22999954223633</v>
       </c>
       <c r="I121" t="n">
-        <v>2.227998489419563</v>
+        <v>2.203452111959615</v>
       </c>
       <c r="J121" t="n">
         <v>18</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>33.54999923706055</v>
+        <v>32.70000076293945</v>
       </c>
       <c r="I122" t="n">
-        <v>1.043219099729151</v>
+        <v>1.070336366464775</v>
       </c>
       <c r="J122" t="n">
         <v>18</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>2.825000047683716</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3539822949100208</v>
+        <v>0.3558718933676701</v>
       </c>
       <c r="J124" t="n">
         <v>18</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>21.8799991607666</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="I125" t="n">
-        <v>5.118830178057278</v>
+        <v>5.045044871663794</v>
       </c>
       <c r="J125" t="n">
         <v>18</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1.519999980926514</v>
+        <v>1.539999961853027</v>
       </c>
       <c r="I126" t="n">
-        <v>6.578947450975964</v>
+        <v>6.493506654355598</v>
       </c>
       <c r="J126" t="n">
         <v>18</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>8.819999694824219</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I127" t="n">
-        <v>2.947845906985394</v>
+        <v>2.954545390507408</v>
       </c>
       <c r="J127" t="n">
         <v>18</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2.092000007629395</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I128" t="n">
-        <v>4.41204587301088</v>
+        <v>4.395238294839327</v>
       </c>
       <c r="J128" t="n">
         <v>18</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9.239999771118164</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I129" t="n">
-        <v>3.787878881707432</v>
+        <v>3.804347904958889</v>
       </c>
       <c r="J129" t="n">
         <v>11</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>9.479999542236328</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6329114229666515</v>
+        <v>0.6249999751647324</v>
       </c>
       <c r="J133" t="n">
         <v>11</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>19.63999938964844</v>
+        <v>19.81999969482422</v>
       </c>
       <c r="I134" t="n">
-        <v>2.545824926367017</v>
+        <v>2.522704377894464</v>
       </c>
       <c r="J134" t="n">
         <v>11</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.200000047683716</v>
+        <v>2.299999952316284</v>
       </c>
       <c r="I135" t="n">
-        <v>2.727272668160684</v>
+        <v>2.608695706257524</v>
       </c>
       <c r="J135" t="n">
         <v>11</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>16.26000022888184</v>
+        <v>16.28000068664551</v>
       </c>
       <c r="I136" t="n">
-        <v>3.075030707022222</v>
+        <v>3.071252941716091</v>
       </c>
       <c r="J136" t="n">
         <v>11</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>4.929999828338623</v>
+        <v>4.889999866485596</v>
       </c>
       <c r="I140" t="n">
-        <v>1.926977754723662</v>
+        <v>1.942740339342294</v>
       </c>
       <c r="J140" t="n">
         <v>11</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>6.980000019073486</v>
+        <v>7.039999961853027</v>
       </c>
       <c r="I144" t="n">
-        <v>3.15186245557063</v>
+        <v>3.125000016933138</v>
       </c>
       <c r="J144" t="n">
         <v>11</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>27.54999923706055</v>
+        <v>27.45000076293945</v>
       </c>
       <c r="I145" t="n">
-        <v>2.214156141171219</v>
+        <v>2.222222160458253</v>
       </c>
       <c r="J145" t="n">
         <v>4</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>3.089999914169312</v>
+        <v>3.079999923706055</v>
       </c>
       <c r="I146" t="n">
-        <v>4.854369066878265</v>
+        <v>4.870129990766698</v>
       </c>
       <c r="J146" t="n">
         <v>4</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>12.10000038146973</v>
+        <v>12.25</v>
       </c>
       <c r="I147" t="n">
-        <v>5.785123784557885</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="J147" t="n">
         <v>4</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>9.159999847412109</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="I148" t="n">
-        <v>5.573144197641301</v>
+        <v>5.536876195389864</v>
       </c>
       <c r="J148" t="n">
         <v>4</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>7.989999771118164</v>
+        <v>8</v>
       </c>
       <c r="I149" t="n">
-        <v>3.379224126838927</v>
+        <v>3.375</v>
       </c>
       <c r="J149" t="n">
         <v>4</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>5.75</v>
+        <v>5.744999885559082</v>
       </c>
       <c r="I150" t="n">
-        <v>6.08695652173913</v>
+        <v>6.092254255387845</v>
       </c>
       <c r="J150" t="n">
         <v>4</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>18.95000076293945</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="I152" t="n">
-        <v>3.957783481817986</v>
+        <v>3.97877976032976</v>
       </c>
       <c r="J152" t="n">
         <v>4</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>11.80000019073486</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I153" t="n">
-        <v>3.644067737707562</v>
+        <v>3.675213735127469</v>
       </c>
       <c r="J153" t="n">
         <v>4</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>4.204999923706055</v>
+        <v>4.260000228881836</v>
       </c>
       <c r="I154" t="n">
-        <v>3.567181990999854</v>
+        <v>3.521126571379833</v>
       </c>
       <c r="J154" t="n">
         <v>4</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>12.30000019073486</v>
+        <v>12.11999988555908</v>
       </c>
       <c r="I155" t="n">
-        <v>1.60299997514244</v>
+        <v>1.626806946053901</v>
       </c>
       <c r="J155" t="n">
         <v>4</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>52.5</v>
+        <v>55.09999847412109</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8952380952380952</v>
+        <v>0.8529945789757973</v>
       </c>
       <c r="J157" t="n">
         <v>4</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>79.69999694824219</v>
+        <v>78.80000305175781</v>
       </c>
       <c r="I158" t="n">
-        <v>1.505646230801351</v>
+        <v>1.522842580617427</v>
       </c>
       <c r="J158" t="n">
         <v>4</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>25.35000038146973</v>
+        <v>25.5</v>
       </c>
       <c r="I159" t="n">
-        <v>1.065088741368871</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="J159" t="n">
         <v>4</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>10.44999980926514</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I160" t="n">
-        <v>3.636363702735056</v>
+        <v>3.689320320030873</v>
       </c>
       <c r="J160" t="n">
         <v>4</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>30.04999923706055</v>
+        <v>30.20000076293945</v>
       </c>
       <c r="I161" t="n">
-        <v>0.9983361318359408</v>
+        <v>0.9933774583481174</v>
       </c>
       <c r="J161" t="n">
         <v>4</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>0.1816000044345856</v>
+        <v>0.1860000044107437</v>
       </c>
       <c r="I162" t="n">
-        <v>3.854625456532674</v>
+        <v>3.763440770970039</v>
       </c>
       <c r="J162" t="n">
         <v>-3</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>7.070000171661377</v>
+        <v>7.21999979019165</v>
       </c>
       <c r="I163" t="n">
-        <v>2.26308339625403</v>
+        <v>2.216066546391865</v>
       </c>
       <c r="J163" t="n">
         <v>-3</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>2.174999952316284</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I164" t="n">
-        <v>2.988505812645086</v>
+        <v>2.954545390507408</v>
       </c>
       <c r="J164" t="n">
         <v>-3</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>7.389999866485596</v>
+        <v>7.440000057220459</v>
       </c>
       <c r="I165" t="n">
-        <v>3.382949993460427</v>
+        <v>3.360215027920289</v>
       </c>
       <c r="J165" t="n">
         <v>-3</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>6.590000152587891</v>
+        <v>6.659999847412109</v>
       </c>
       <c r="I167" t="n">
-        <v>7.587253238585285</v>
+        <v>7.507507679512727</v>
       </c>
       <c r="J167" t="n">
         <v>-10</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>18.52000045776367</v>
+        <v>18.6299991607666</v>
       </c>
       <c r="I168" t="n">
-        <v>3.509719135711559</v>
+        <v>3.488996399789711</v>
       </c>
       <c r="J168" t="n">
         <v>-10</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>12.1850004196167</v>
+        <v>12.38500022888184</v>
       </c>
       <c r="I169" t="n">
-        <v>4.431678140368802</v>
+        <v>4.360112959390339</v>
       </c>
       <c r="J169" t="n">
         <v>-10</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>6.168000221252441</v>
+        <v>6.300000190734863</v>
       </c>
       <c r="I170" t="n">
-        <v>1.621271018367352</v>
+        <v>1.587301539245438</v>
       </c>
       <c r="J170" t="n">
         <v>-10</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>9.199999809265137</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="I171" t="n">
-        <v>1.739130470838349</v>
+        <v>1.731601774494826</v>
       </c>
       <c r="J171" t="n">
         <v>-10</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>287.3999938964844</v>
+        <v>293.3500061035156</v>
       </c>
       <c r="I172" t="n">
-        <v>1.257828836733396</v>
+        <v>1.232316320022288</v>
       </c>
       <c r="J172" t="n">
         <v>-10</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>30</v>
+        <v>30.89999961853027</v>
       </c>
       <c r="I173" t="n">
-        <v>4.533333333333333</v>
+        <v>4.401294552717173</v>
       </c>
       <c r="J173" t="n">
         <v>-10</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>13.97500038146973</v>
+        <v>13.96500015258789</v>
       </c>
       <c r="I174" t="n">
-        <v>41.65724394340054</v>
+        <v>41.68707437444019</v>
       </c>
       <c r="J174" t="n">
         <v>-10</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>15.63000011444092</v>
+        <v>15.69999980926514</v>
       </c>
       <c r="I175" t="n">
-        <v>3.742802275858623</v>
+        <v>3.726114694949043</v>
       </c>
       <c r="J175" t="n">
         <v>-10</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>19.57999992370605</v>
+        <v>19.84499931335449</v>
       </c>
       <c r="I176" t="n">
-        <v>3.217568960443362</v>
+        <v>3.174603284445809</v>
       </c>
       <c r="J176" t="n">
         <v>-10</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>128.3000030517578</v>
+        <v>127.9499969482422</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7014808874454421</v>
+        <v>0.7033997823103226</v>
       </c>
       <c r="J177" t="n">
         <v>-10</v>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>64.25</v>
+        <v>65.62000274658203</v>
       </c>
       <c r="I178" t="n">
-        <v>2.678287937743191</v>
+        <v>2.622371118522441</v>
       </c>
       <c r="J178" t="n">
         <v>-10</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>26.20000076293945</v>
+        <v>26.79999923706055</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5343511294779558</v>
+        <v>0.5223880745727789</v>
       </c>
       <c r="J179" t="n">
         <v>-17</v>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>1.570000052452087</v>
+        <v>1.529999971389771</v>
       </c>
       <c r="I180" t="n">
-        <v>3.821655923277815</v>
+        <v>3.92156870078234</v>
       </c>
       <c r="J180" t="n">
         <v>-17</v>
@@ -8912,7 +8912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C415"/>
+  <dimension ref="A1:C425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9003,7 +9003,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9020,7 +9020,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -9030,14 +9030,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9047,14 +9047,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9071,7 +9071,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9581,7 +9581,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9717,7 +9717,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9802,7 +9802,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9955,7 +9955,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9972,7 +9972,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9989,7 +9989,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -10006,7 +10006,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -10023,7 +10023,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -10040,7 +10040,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -10057,7 +10057,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10091,7 +10091,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -10108,7 +10108,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -10125,7 +10125,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10142,7 +10142,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10152,14 +10152,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10169,14 +10169,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10193,7 +10193,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10210,7 +10210,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10244,7 +10244,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10254,14 +10254,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10271,14 +10271,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10288,14 +10288,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10305,14 +10305,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10322,14 +10322,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10346,7 +10346,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10356,36 +10356,36 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -10397,29 +10397,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -10431,12 +10431,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -10448,12 +10448,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10465,63 +10465,63 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10533,7 +10533,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10543,14 +10543,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10560,14 +10560,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10577,14 +10577,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10601,7 +10601,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10618,7 +10618,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10628,14 +10628,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10645,14 +10645,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10662,14 +10662,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10686,7 +10686,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10696,14 +10696,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10713,14 +10713,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10737,7 +10737,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10747,19 +10747,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -10771,80 +10771,80 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -10856,29 +10856,29 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -10890,29 +10890,29 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -10924,7 +10924,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10934,14 +10934,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10958,7 +10958,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10968,14 +10968,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10985,14 +10985,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11002,14 +11002,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11019,14 +11019,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11036,14 +11036,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11053,14 +11053,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11077,7 +11077,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11094,7 +11094,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11104,14 +11104,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11121,14 +11121,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11138,14 +11138,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11155,14 +11155,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11172,53 +11172,53 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -11230,46 +11230,46 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -11281,29 +11281,29 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -11315,41 +11315,41 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11366,7 +11366,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11383,7 +11383,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11400,7 +11400,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11410,14 +11410,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11427,14 +11427,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11451,7 +11451,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11461,14 +11461,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11485,7 +11485,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11502,7 +11502,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11512,14 +11512,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11529,14 +11529,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11546,14 +11546,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11563,14 +11563,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11580,14 +11580,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11604,7 +11604,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11621,7 +11621,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11631,14 +11631,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11648,14 +11648,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11665,14 +11665,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11689,7 +11689,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11706,7 +11706,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11716,14 +11716,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11740,7 +11740,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11757,7 +11757,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11808,7 +11808,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11825,7 +11825,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11842,7 +11842,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11852,14 +11852,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11869,14 +11869,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11886,19 +11886,19 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11910,29 +11910,29 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11944,80 +11944,80 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -12029,41 +12029,41 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12073,14 +12073,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12090,19 +12090,19 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -12114,12 +12114,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -12131,12 +12131,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12148,46 +12148,46 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12199,97 +12199,97 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12301,63 +12301,63 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12369,29 +12369,29 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12403,29 +12403,29 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12437,7 +12437,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12454,7 +12454,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12464,14 +12464,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12481,14 +12481,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12505,7 +12505,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12522,7 +12522,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12532,14 +12532,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12549,14 +12549,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12566,14 +12566,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12583,14 +12583,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12607,7 +12607,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12617,14 +12617,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12634,14 +12634,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12651,14 +12651,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12675,7 +12675,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12685,14 +12685,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12702,14 +12702,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12726,7 +12726,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12736,104 +12736,104 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -12845,75 +12845,75 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12923,14 +12923,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12947,7 +12947,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12964,7 +12964,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12974,14 +12974,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12998,7 +12998,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -13008,14 +13008,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -13032,7 +13032,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -13042,14 +13042,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -13059,14 +13059,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -13076,14 +13076,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13093,14 +13093,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13110,14 +13110,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13127,14 +13127,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13151,7 +13151,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13168,7 +13168,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13178,14 +13178,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13202,7 +13202,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13229,14 +13229,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13253,7 +13253,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13270,7 +13270,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13287,7 +13287,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13304,7 +13304,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13321,7 +13321,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13331,19 +13331,19 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -13355,12 +13355,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -13372,46 +13372,46 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -13423,12 +13423,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -13440,29 +13440,29 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -13474,29 +13474,29 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -13508,7 +13508,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13525,7 +13525,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13542,7 +13542,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13552,14 +13552,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13569,14 +13569,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13586,14 +13586,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13610,7 +13610,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13620,14 +13620,14 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13644,7 +13644,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13661,7 +13661,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13678,7 +13678,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13695,7 +13695,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13712,7 +13712,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13729,7 +13729,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13746,7 +13746,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13756,14 +13756,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13780,7 +13780,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13790,14 +13790,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13814,7 +13814,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13831,7 +13831,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13848,7 +13848,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13865,7 +13865,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13875,14 +13875,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13892,14 +13892,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13909,14 +13909,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13933,7 +13933,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13950,7 +13950,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13967,7 +13967,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13984,7 +13984,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13994,14 +13994,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -14011,14 +14011,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -14035,7 +14035,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -14045,14 +14045,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -14062,14 +14062,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -14086,7 +14086,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -14103,7 +14103,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -14120,7 +14120,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -14130,14 +14130,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14154,7 +14154,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -14164,14 +14164,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14188,7 +14188,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14198,14 +14198,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14215,19 +14215,19 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -14239,12 +14239,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -14256,29 +14256,29 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -14290,12 +14290,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -14307,29 +14307,29 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -14341,29 +14341,29 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -14375,12 +14375,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -14392,7 +14392,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14409,7 +14409,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14426,7 +14426,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14436,14 +14436,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14453,14 +14453,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14470,14 +14470,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14487,14 +14487,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14511,7 +14511,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14528,7 +14528,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14538,14 +14538,14 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14555,14 +14555,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14579,7 +14579,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14589,14 +14589,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14606,14 +14606,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14623,36 +14623,36 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -14664,12 +14664,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -14681,29 +14681,29 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -14715,46 +14715,46 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -14766,29 +14766,29 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -14800,63 +14800,63 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -14868,46 +14868,46 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -14919,29 +14919,29 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -14953,46 +14953,46 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -15004,34 +15004,34 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -15055,29 +15055,29 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -15089,29 +15089,29 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -15123,63 +15123,63 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -15191,46 +15191,46 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -15242,114 +15242,114 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>TALEA GROUP</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -15361,12 +15361,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -15378,12 +15378,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -15395,12 +15395,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -15412,12 +15412,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -15429,46 +15429,46 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -15480,29 +15480,29 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>TALEA GROUP</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -15514,12 +15514,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -15531,63 +15531,63 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -15599,12 +15599,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -15616,41 +15616,41 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15660,14 +15660,14 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15684,7 +15684,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15694,24 +15694,24 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -15735,80 +15735,80 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -15820,12 +15820,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -15837,12 +15837,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -15854,12 +15854,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -15871,7 +15871,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15888,7 +15888,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15898,14 +15898,14 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15915,14 +15915,14 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15932,39 +15932,209 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
+          <t>Gentili Mosconi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>E-Globe S.p.A.</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>TMP Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Adventure S.p.A.</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Triboo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Vantea Smart S.p.A.</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Cloudia Research S.p.A.</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>TMP Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
           <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
+      <c r="B425" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr">
+      <c r="C425" t="inlineStr">
         <is>
           <t>Bod Annual Report</t>
         </is>
@@ -15994,61 +16164,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TMP Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>